--- a/data/trending_integrated_20260915_09.xlsx
+++ b/data/trending_integrated_20260915_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z6"/>
+  <dimension ref="A1:Z9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10820</v>
+        <v>10950</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+5.36%</t>
+          <t>'+6.62%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0.26</v>
       </c>
       <c r="E2" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="F2" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="G2" t="n">
-        <v>132</v>
+        <v>152</v>
       </c>
       <c r="H2" t="n">
         <v>17.93</v>
@@ -601,7 +601,7 @@
         <v>11000</v>
       </c>
       <c r="L2" t="n">
-        <v>11200</v>
+        <v>11650</v>
       </c>
       <c r="M2" t="n">
         <v>10710</v>
@@ -610,7 +610,7 @@
         <v>17.67</v>
       </c>
       <c r="O2" t="n">
-        <v>25064995775</v>
+        <v>119373192755</v>
       </c>
       <c r="P2" t="n">
         <v>22450</v>
@@ -626,12 +626,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>광통신 CPO, microled 관련 미국 기업과 594억 공급계약 체결. 트럼프 AI 정책 수혜 기대감에 따른 주가 상승 전망.</t>
+          <t>광통신 대장주로서 미국 기업과의 594억 공급 계약 발표 및 트럼프 AI 정책 강화 기대감으로 인한 급등 전망. 광통신 섹터 전반의 상승 추세와 기타법인 매수세 유입이 긍정적 요인.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>30750</v>
+        <v>15290</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+1.32%</t>
+          <t>'+4.30%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.05</v>
+        <v>-1.17</v>
       </c>
       <c r="E3" t="n">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="F3" t="n">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="G3" t="n">
-        <v>322</v>
+        <v>223</v>
       </c>
       <c r="H3" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,28 +687,28 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>30350</v>
+        <v>14660</v>
       </c>
       <c r="K3" t="n">
-        <v>30250</v>
+        <v>14980</v>
       </c>
       <c r="L3" t="n">
-        <v>30750</v>
+        <v>15460</v>
       </c>
       <c r="M3" t="n">
-        <v>30250</v>
+        <v>14330</v>
       </c>
       <c r="N3" t="n">
-        <v>17.55</v>
+        <v>1.17</v>
       </c>
       <c r="O3" t="n">
-        <v>537338850</v>
+        <v>18782357820</v>
       </c>
       <c r="P3" t="n">
-        <v>69200</v>
+        <v>36200</v>
       </c>
       <c r="Q3" t="n">
-        <v>24150</v>
+        <v>8920</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>HLB 제약 유증, 리보세라닙 FDA 승인 관련 불확실성 지속. 임상 결과 및 공시 발표 지연으로 인한 투자 심리 위축.</t>
+          <t>이란 관련 지정학적 리스크와 국제 유가 상승 기대감으로 인한 주가 상승 가능성. 중국의 원유 매수 및 중동 지역 긴장 고조가 유가 상승 요인으로 작용하며 흥구석유에 긍정적 영향.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,11 +727,11 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['리보세라닙', 'FDA 승인', '유증']</t>
+          <t>['유가', '이란', '지정학']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1706000</v>
+        <v>141300</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+0.53%</t>
+          <t>'+3.37%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.2</v>
+        <v>0.05</v>
       </c>
       <c r="E4" t="n">
-        <v>800</v>
+        <v>58</v>
       </c>
       <c r="F4" t="n">
-        <v>503</v>
+        <v>36</v>
       </c>
       <c r="G4" t="n">
-        <v>2707</v>
+        <v>119</v>
       </c>
       <c r="H4" t="n">
-        <v>50.27</v>
+        <v>15.81</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,28 +779,28 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1697000</v>
+        <v>136700</v>
       </c>
       <c r="K4" t="n">
-        <v>1690000</v>
+        <v>139500</v>
       </c>
       <c r="L4" t="n">
-        <v>1707000</v>
+        <v>144100</v>
       </c>
       <c r="M4" t="n">
-        <v>1690000</v>
+        <v>138800</v>
       </c>
       <c r="N4" t="n">
-        <v>50.47</v>
+        <v>15.76</v>
       </c>
       <c r="O4" t="n">
-        <v>253697289500</v>
+        <v>33870730450</v>
       </c>
       <c r="P4" t="n">
-        <v>2987000</v>
+        <v>164700</v>
       </c>
       <c r="Q4" t="n">
-        <v>325000</v>
+        <v>87700</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>미국 반도체 지수 폭락 및 국채 금리 5% 돌파로 인한 투자 심리 위축. 단기 반등 가능성 언급.</t>
+          <t>합병 관련 불확실성과 시장 변동성에 대한 우려가 공존하는 상황. 목표가 상향 및 실적 개선 기대감도 있으나, 하락 압력 또한 상존하며 방향성 탐색 중.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,11 +819,11 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['반도체', '국채 금리', '폭락']</t>
+          <t>['합병', '실적', '변동성']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,67 +832,67 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>096770</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>224500</v>
+        <v>30900</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'-0.22%</t>
+          <t>'+1.81%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.15</v>
+        <v>-0.05</v>
       </c>
       <c r="E5" t="n">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="F5" t="n">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="G5" t="n">
-        <v>253</v>
+        <v>351</v>
       </c>
       <c r="H5" t="n">
-        <v>7.2</v>
+        <v>17.5</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>225000</v>
+        <v>30350</v>
       </c>
       <c r="K5" t="n">
-        <v>228500</v>
+        <v>30250</v>
       </c>
       <c r="L5" t="n">
-        <v>229000</v>
+        <v>31100</v>
       </c>
       <c r="M5" t="n">
-        <v>224000</v>
+        <v>30250</v>
       </c>
       <c r="N5" t="n">
-        <v>7.05</v>
+        <v>17.55</v>
       </c>
       <c r="O5" t="n">
-        <v>13530891250</v>
+        <v>1394684375</v>
       </c>
       <c r="P5" t="n">
-        <v>426000</v>
+        <v>69200</v>
       </c>
       <c r="Q5" t="n">
-        <v>89500</v>
+        <v>24150</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -902,20 +902,20 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>머스크의 테라팹에 패키징 장비 공급 계약 체결 사실 부각. 공매도 세력에 대한 경계심 속 주가 상승 기대.</t>
+          <t>HLB의 FDA 승인 기대감에도 불구하고, 부정적 결과 및 제약 유증 관련 이슈로 인한 하락세 지속. 기관 및 외인 이탈 움직임과 함께 주가 하락에 대한 우려가 높은 상황.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['테라팹', '패키징 장비', '공급 계약']</t>
+          <t>['FDA', '신약', '하락']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,67 +924,67 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>042700</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14420</v>
+        <v>1698000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-1.64%</t>
+          <t>'+0.06%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-1.17</v>
+        <v>-0.2</v>
       </c>
       <c r="E6" t="n">
-        <v>73</v>
+        <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>55</v>
+        <v>506</v>
       </c>
       <c r="G6" t="n">
-        <v>201</v>
+        <v>2616</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>50.27</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>14660</v>
+        <v>1697000</v>
       </c>
       <c r="K6" t="n">
-        <v>14980</v>
+        <v>1690000</v>
       </c>
       <c r="L6" t="n">
-        <v>15030</v>
+        <v>1707000</v>
       </c>
       <c r="M6" t="n">
-        <v>14340</v>
+        <v>1685000</v>
       </c>
       <c r="N6" t="n">
-        <v>1.17</v>
+        <v>50.47</v>
       </c>
       <c r="O6" t="n">
-        <v>3856626860</v>
+        <v>485500712000</v>
       </c>
       <c r="P6" t="n">
-        <v>36200</v>
+        <v>2987000</v>
       </c>
       <c r="Q6" t="n">
-        <v>8920</v>
+        <v>325000</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -994,29 +994,305 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>중동 지역 지정학적 리스크 고조에 따른 국제유가 상승 및 유가 120불 이상 전망. 해상 운임 상승 영향 언급.</t>
+          <t>미국 필라델피아 반도체 지수 폭락 및 국내외 금리 상승 우려로 인한 하락세 지속 가능성 언급. 하지만 일부에서는 반등 가능성도 제기되며, 시장 전반의 투자 심리 위축이 반영됨.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>['반도체', '금리', '하락']</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>71</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>000660</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>248500</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>'-0.20%</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="E7" t="n">
+        <v>789</v>
+      </c>
+      <c r="F7" t="n">
+        <v>475</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2923</v>
+      </c>
+      <c r="H7" t="n">
+        <v>46.57</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>249000</v>
+      </c>
+      <c r="K7" t="n">
+        <v>248000</v>
+      </c>
+      <c r="L7" t="n">
+        <v>250000</v>
+      </c>
+      <c r="M7" t="n">
+        <v>247500</v>
+      </c>
+      <c r="N7" t="n">
+        <v>46.64</v>
+      </c>
+      <c r="O7" t="n">
+        <v>247305203250</v>
+      </c>
+      <c r="P7" t="n">
+        <v>374500</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>75900</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>트럼프 AI 관련 긍정적 언급에도 불구하고, 국내 정치적 이슈와 일부 부정적 전망이 혼재하며 보합세를 보이는 상황. 미 증시 반도체 섹터의 움직임이 중요 변수로 작용.</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>['반도체', 'AI', '정치']</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>106</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>두산에너빌리티</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>85300</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>'-1.95%</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="E8" t="n">
+        <v>65</v>
+      </c>
+      <c r="F8" t="n">
+        <v>46</v>
+      </c>
+      <c r="G8" t="n">
+        <v>415</v>
+      </c>
+      <c r="H8" t="n">
+        <v>23.45</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>87000</v>
+      </c>
+      <c r="K8" t="n">
+        <v>86200</v>
+      </c>
+      <c r="L8" t="n">
+        <v>86500</v>
+      </c>
+      <c r="M8" t="n">
+        <v>85200</v>
+      </c>
+      <c r="N8" t="n">
+        <v>23.56</v>
+      </c>
+      <c r="O8" t="n">
+        <v>23126818950</v>
+      </c>
+      <c r="P8" t="n">
+        <v>139200</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>57000</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>두산에너빌리티의 상승 가능성 및 원전 관련 긍정적 뉴스 언급. 엑스에너지 급등과 원전 ETF 추가 출시 등 우호적인 시장 환경이 주가 상승을 견인할 것으로 기대.</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>['원전', '에너지', '상승']</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>034020</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>한미반도체</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>219500</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>'-2.44%</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E9" t="n">
+        <v>70</v>
+      </c>
+      <c r="F9" t="n">
+        <v>49</v>
+      </c>
+      <c r="G9" t="n">
+        <v>294</v>
+      </c>
+      <c r="H9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>225000</v>
+      </c>
+      <c r="K9" t="n">
+        <v>228500</v>
+      </c>
+      <c r="L9" t="n">
+        <v>229000</v>
+      </c>
+      <c r="M9" t="n">
+        <v>219500</v>
+      </c>
+      <c r="N9" t="n">
+        <v>7.05</v>
+      </c>
+      <c r="O9" t="n">
+        <v>29333089500</v>
+      </c>
+      <c r="P9" t="n">
+        <v>426000</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>89500</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>일론 머스크의 테라팹에 대한 한미반도체 패키징 장비 공급 사실 확인 및 공시 가능성으로 인한 강한 상승 기대감. 공매도 세력과의 대립 구도 속에서 주가 급등 가능성 언급.</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="n">
         <v>0.5</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>['국제유가', '지정학적 리스크', '해상 운임']</t>
-        </is>
-      </c>
-      <c r="X6" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y6" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>['반도체', '테라팹', '공매도']</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y9" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>024060</t>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>042700</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20260915_09.xlsx
+++ b/data/trending_integrated_20260915_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z9"/>
+  <dimension ref="A1:Z11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10950</v>
+        <v>10560</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+6.62%</t>
+          <t>'+2.82%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0.26</v>
       </c>
       <c r="E2" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F2" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G2" t="n">
-        <v>152</v>
+        <v>172</v>
       </c>
       <c r="H2" t="n">
         <v>17.93</v>
@@ -604,13 +604,13 @@
         <v>11650</v>
       </c>
       <c r="M2" t="n">
-        <v>10710</v>
+        <v>10430</v>
       </c>
       <c r="N2" t="n">
         <v>17.67</v>
       </c>
       <c r="O2" t="n">
-        <v>119373192755</v>
+        <v>151905496410</v>
       </c>
       <c r="P2" t="n">
         <v>22450</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>광통신 대장주로서 미국 기업과의 594억 공급 계약 발표 및 트럼프 AI 정책 강화 기대감으로 인한 급등 전망. 광통신 섹터 전반의 상승 추세와 기타법인 매수세 유입이 긍정적 요인.</t>
+          <t>트럼프 AI 정책 기대감과 미국 광통신주 급등에 따른 동반 상승 전망. 기타법인 매수세 유입.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['광통신', 'CPO', 'AI']</t>
+          <t>['광통신', 'AI', '트럼프']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15290</v>
+        <v>31100</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+4.30%</t>
+          <t>'+2.47%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-1.17</v>
+        <v>-0.05</v>
       </c>
       <c r="E3" t="n">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="F3" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="G3" t="n">
-        <v>223</v>
+        <v>399</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,28 +687,28 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>14660</v>
+        <v>30350</v>
       </c>
       <c r="K3" t="n">
-        <v>14980</v>
+        <v>30250</v>
       </c>
       <c r="L3" t="n">
-        <v>15460</v>
+        <v>31500</v>
       </c>
       <c r="M3" t="n">
-        <v>14330</v>
+        <v>30250</v>
       </c>
       <c r="N3" t="n">
-        <v>1.17</v>
+        <v>17.55</v>
       </c>
       <c r="O3" t="n">
-        <v>18782357820</v>
+        <v>2537068400</v>
       </c>
       <c r="P3" t="n">
-        <v>36200</v>
+        <v>69200</v>
       </c>
       <c r="Q3" t="n">
-        <v>8920</v>
+        <v>24150</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -718,20 +718,20 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>이란 관련 지정학적 리스크와 국제 유가 상승 기대감으로 인한 주가 상승 가능성. 중국의 원유 매수 및 중동 지역 긴장 고조가 유가 상승 요인으로 작용하며 흥구석유에 긍정적 영향.</t>
+          <t>리보세라닙 담관암 FDA 승인 기대감과 주가 급락 상황 공존. 제약 유증 및 기관외인 매도세.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['유가', '이란', '지정학']</t>
+          <t>['FDA', '담관암', '신약']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,67 +740,67 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>141300</v>
+        <v>15010</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+3.37%</t>
+          <t>'+2.39%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.05</v>
+        <v>-1.17</v>
       </c>
       <c r="E4" t="n">
-        <v>58</v>
+        <v>97</v>
       </c>
       <c r="F4" t="n">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="G4" t="n">
-        <v>119</v>
+        <v>242</v>
       </c>
       <c r="H4" t="n">
-        <v>15.81</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>136700</v>
+        <v>14660</v>
       </c>
       <c r="K4" t="n">
-        <v>139500</v>
+        <v>14980</v>
       </c>
       <c r="L4" t="n">
-        <v>144100</v>
+        <v>15460</v>
       </c>
       <c r="M4" t="n">
-        <v>138800</v>
+        <v>14330</v>
       </c>
       <c r="N4" t="n">
-        <v>15.76</v>
+        <v>1.17</v>
       </c>
       <c r="O4" t="n">
-        <v>33870730450</v>
+        <v>23166844695</v>
       </c>
       <c r="P4" t="n">
-        <v>164700</v>
+        <v>36200</v>
       </c>
       <c r="Q4" t="n">
-        <v>87700</v>
+        <v>8920</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -810,20 +810,20 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>합병 관련 불확실성과 시장 변동성에 대한 우려가 공존하는 상황. 목표가 상향 및 실적 개선 기대감도 있으나, 하락 압력 또한 상존하며 방향성 탐색 중.</t>
+          <t>이란 관련 지정학적 리스크 및 국제유가 상승 기대감 반영. 미국과의 단계적 협상 합의 추진 소식.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['합병', '실적', '변동성']</t>
+          <t>['국제유가', '이란', '지정학적 리스크']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,67 +832,67 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>30900</v>
+        <v>139800</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+1.81%</t>
+          <t>'+2.27%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.05</v>
+        <v>0.05</v>
       </c>
       <c r="E5" t="n">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="F5" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="G5" t="n">
-        <v>351</v>
+        <v>134</v>
       </c>
       <c r="H5" t="n">
-        <v>17.5</v>
+        <v>15.81</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>30350</v>
+        <v>136700</v>
       </c>
       <c r="K5" t="n">
-        <v>30250</v>
+        <v>139500</v>
       </c>
       <c r="L5" t="n">
-        <v>31100</v>
+        <v>144100</v>
       </c>
       <c r="M5" t="n">
-        <v>30250</v>
+        <v>138800</v>
       </c>
       <c r="N5" t="n">
-        <v>17.55</v>
+        <v>15.76</v>
       </c>
       <c r="O5" t="n">
-        <v>1394684375</v>
+        <v>44119707100</v>
       </c>
       <c r="P5" t="n">
-        <v>69200</v>
+        <v>164700</v>
       </c>
       <c r="Q5" t="n">
-        <v>24150</v>
+        <v>87700</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>HLB의 FDA 승인 기대감에도 불구하고, 부정적 결과 및 제약 유증 관련 이슈로 인한 하락세 지속. 기관 및 외인 이탈 움직임과 함께 주가 하락에 대한 우려가 높은 상황.</t>
+          <t>영업이익 10조 전망 및 목표가 상향 리포트 등장, 기술적 반등 기대. 합병 관련 정보와 주가 흔들림.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['FDA', '신약', '하락']</t>
+          <t>['영업이익', '합병', '리포트']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -924,7 +924,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>096770</t>
         </is>
       </c>
     </row>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1698000</v>
+        <v>1707000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+0.06%</t>
+          <t>'+0.59%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -949,10 +949,10 @@
         <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>506</v>
+        <v>496</v>
       </c>
       <c r="G6" t="n">
-        <v>2616</v>
+        <v>2430</v>
       </c>
       <c r="H6" t="n">
         <v>50.27</v>
@@ -969,7 +969,7 @@
         <v>1690000</v>
       </c>
       <c r="L6" t="n">
-        <v>1707000</v>
+        <v>1713000</v>
       </c>
       <c r="M6" t="n">
         <v>1685000</v>
@@ -978,7 +978,7 @@
         <v>50.47</v>
       </c>
       <c r="O6" t="n">
-        <v>485500712000</v>
+        <v>662895910500</v>
       </c>
       <c r="P6" t="n">
         <v>2987000</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>미국 필라델피아 반도체 지수 폭락 및 국내외 금리 상승 우려로 인한 하락세 지속 가능성 언급. 하지만 일부에서는 반등 가능성도 제기되며, 시장 전반의 투자 심리 위축이 반영됨.</t>
+          <t>트럼프 AI 규제 우려 및 미국 10년물 국채 금리 상승에 따른 변동성 예상. 일부 투자자 반등 기대.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['반도체', '금리', '하락']</t>
+          <t>['AI', '반도체', '트럼프']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>248500</v>
+        <v>249750</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-0.20%</t>
+          <t>'+0.30%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>789</v>
+        <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="G7" t="n">
-        <v>2923</v>
+        <v>2769</v>
       </c>
       <c r="H7" t="n">
         <v>46.57</v>
@@ -1070,7 +1070,7 @@
         <v>46.64</v>
       </c>
       <c r="O7" t="n">
-        <v>247305203250</v>
+        <v>341086649250</v>
       </c>
       <c r="P7" t="n">
         <v>374500</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>트럼프 AI 관련 긍정적 언급에도 불구하고, 국내 정치적 이슈와 일부 부정적 전망이 혼재하며 보합세를 보이는 상황. 미 증시 반도체 섹터의 움직임이 중요 변수로 작용.</t>
+          <t>트럼프 AI 관련 발언과 미국 증시 반등에 따른 국내 증시 및 반도체주 동반 상승 기대. 일부 투자자 반등 예상.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['반도체', 'AI', '정치']</t>
+          <t>['AI', '반도체', '트럼프']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1115,31 +1115,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>한미반도체</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>85300</v>
+        <v>223500</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-1.95%</t>
+          <t>'-0.67%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.11</v>
+        <v>0.15</v>
       </c>
       <c r="E8" t="n">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="F8" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="G8" t="n">
-        <v>415</v>
+        <v>396</v>
       </c>
       <c r="H8" t="n">
-        <v>23.45</v>
+        <v>7.2</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,28 +1147,28 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>87000</v>
+        <v>225000</v>
       </c>
       <c r="K8" t="n">
-        <v>86200</v>
+        <v>228500</v>
       </c>
       <c r="L8" t="n">
-        <v>86500</v>
+        <v>229000</v>
       </c>
       <c r="M8" t="n">
-        <v>85200</v>
+        <v>219500</v>
       </c>
       <c r="N8" t="n">
-        <v>23.56</v>
+        <v>7.05</v>
       </c>
       <c r="O8" t="n">
-        <v>23126818950</v>
+        <v>34303493750</v>
       </c>
       <c r="P8" t="n">
-        <v>139200</v>
+        <v>426000</v>
       </c>
       <c r="Q8" t="n">
-        <v>57000</v>
+        <v>89500</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1178,20 +1178,20 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>두산에너빌리티의 상승 가능성 및 원전 관련 긍정적 뉴스 언급. 엑스에너지 급등과 원전 ETF 추가 출시 등 우호적인 시장 환경이 주가 상승을 견인할 것으로 기대.</t>
+          <t>머스크 테라팹 공급 계약 체결 뉴스 부각. AI 반도체 관련 성장성 기대감과 함께 공매도 세력과의 공방.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['원전', '에너지', '상승']</t>
+          <t>['AI', '반도체', '테라팹']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>042700</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>219500</v>
+        <v>85500</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-2.44%</t>
+          <t>'-1.72%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.15</v>
+        <v>-0.11</v>
       </c>
       <c r="E9" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="F9" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G9" t="n">
-        <v>294</v>
+        <v>437</v>
       </c>
       <c r="H9" t="n">
-        <v>7.2</v>
+        <v>23.45</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,28 +1239,28 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>225000</v>
+        <v>87000</v>
       </c>
       <c r="K9" t="n">
-        <v>228500</v>
+        <v>86200</v>
       </c>
       <c r="L9" t="n">
-        <v>229000</v>
+        <v>86500</v>
       </c>
       <c r="M9" t="n">
-        <v>219500</v>
+        <v>85000</v>
       </c>
       <c r="N9" t="n">
-        <v>7.05</v>
+        <v>23.56</v>
       </c>
       <c r="O9" t="n">
-        <v>29333089500</v>
+        <v>30698139350</v>
       </c>
       <c r="P9" t="n">
-        <v>426000</v>
+        <v>139200</v>
       </c>
       <c r="Q9" t="n">
-        <v>89500</v>
+        <v>57000</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>일론 머스크의 테라팹에 대한 한미반도체 패키징 장비 공급 사실 확인 및 공시 가능성으로 인한 강한 상승 기대감. 공매도 세력과의 대립 구도 속에서 주가 급등 가능성 언급.</t>
+          <t>X에너지 급등 및 원전 관련 긍정적 뉴스에 따른 동반 상승 기대. 원전 ETF 추가 출시 및 신용 매수 유입.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,20 +1279,204 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['반도체', '테라팹', '공매도']</t>
+          <t>['원전', '에너지', 'ETF']</t>
         </is>
       </c>
       <c r="X9" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>034020</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>대한광통신</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>14100</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>'-2.69%</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="E10" t="n">
+        <v>46</v>
+      </c>
+      <c r="F10" t="n">
+        <v>32</v>
+      </c>
+      <c r="G10" t="n">
+        <v>207</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>14490</v>
+      </c>
+      <c r="K10" t="n">
+        <v>14410</v>
+      </c>
+      <c r="L10" t="n">
+        <v>14600</v>
+      </c>
+      <c r="M10" t="n">
+        <v>13930</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="O10" t="n">
+        <v>21734815670</v>
+      </c>
+      <c r="P10" t="n">
+        <v>31500</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1272</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>미국 광통신 대장주 루멘텀 폭락 및 국내 증시 하락세 반영. 외국인 보유율이 바닥이라 급락 염려 적음.</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>['광통신', '미국증시', '외국인']</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>010170</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>삼성중공업</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>21250</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>'-3.85%</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E11" t="n">
+        <v>43</v>
+      </c>
+      <c r="F11" t="n">
+        <v>31</v>
+      </c>
+      <c r="G11" t="n">
+        <v>104</v>
+      </c>
+      <c r="H11" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>22100</v>
+      </c>
+      <c r="K11" t="n">
+        <v>21850</v>
+      </c>
+      <c r="L11" t="n">
+        <v>21850</v>
+      </c>
+      <c r="M11" t="n">
+        <v>21150</v>
+      </c>
+      <c r="N11" t="n">
+        <v>28.81</v>
+      </c>
+      <c r="O11" t="n">
+        <v>15122311150</v>
+      </c>
+      <c r="P11" t="n">
+        <v>35350</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>18440</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>12억 달러 수주 공시 확인, 코스피 하락 속 주가 상승. 그러나 북극항로 성공 등 뉴스에도 조용하며, 주가 움직임에 대한 불만.</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>['수주', '공시', '북극항로']</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
         <v>2</v>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>042700</t>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>010140</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20260915_09.xlsx
+++ b/data/trending_integrated_20260915_09.xlsx
@@ -563,70 +563,70 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10560</v>
+        <v>31000</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+2.82%</t>
+          <t>'+2.14%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.26</v>
+        <v>-0.05</v>
       </c>
       <c r="E2" t="n">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="F2" t="n">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="G2" t="n">
-        <v>172</v>
+        <v>426</v>
       </c>
       <c r="H2" t="n">
-        <v>17.93</v>
+        <v>17.5</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>10270</v>
+        <v>30350</v>
       </c>
       <c r="K2" t="n">
-        <v>11000</v>
+        <v>30250</v>
       </c>
       <c r="L2" t="n">
-        <v>11650</v>
+        <v>31500</v>
       </c>
       <c r="M2" t="n">
-        <v>10430</v>
+        <v>30250</v>
       </c>
       <c r="N2" t="n">
-        <v>17.67</v>
+        <v>17.55</v>
       </c>
       <c r="O2" t="n">
-        <v>151905496410</v>
+        <v>2825487750</v>
       </c>
       <c r="P2" t="n">
-        <v>22450</v>
+        <v>69200</v>
       </c>
       <c r="Q2" t="n">
-        <v>1760</v>
+        <v>24150</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>18000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>트럼프 AI 정책 기대감과 미국 광통신주 급등에 따른 동반 상승 전망. 기타법인 매수세 유입.</t>
+          <t>FDA 승인 관련 불확실성 및 유증 이슈로 인한 주가 하락과 투자자 불신.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,11 +635,11 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['광통신', 'AI', '트럼프']</t>
+          <t>['FDA', '담관암', '유증']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,86 +648,86 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>31100</v>
+        <v>138900</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+2.47%</t>
+          <t>'+1.61%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.05</v>
+        <v>0.05</v>
       </c>
       <c r="E3" t="n">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="F3" t="n">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="G3" t="n">
-        <v>399</v>
+        <v>156</v>
       </c>
       <c r="H3" t="n">
-        <v>17.5</v>
+        <v>15.81</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>30350</v>
+        <v>136700</v>
       </c>
       <c r="K3" t="n">
-        <v>30250</v>
+        <v>139500</v>
       </c>
       <c r="L3" t="n">
-        <v>31500</v>
+        <v>144100</v>
       </c>
       <c r="M3" t="n">
-        <v>30250</v>
+        <v>138200</v>
       </c>
       <c r="N3" t="n">
-        <v>17.55</v>
+        <v>15.76</v>
       </c>
       <c r="O3" t="n">
-        <v>2537068400</v>
+        <v>51447761500</v>
       </c>
       <c r="P3" t="n">
-        <v>69200</v>
+        <v>164700</v>
       </c>
       <c r="Q3" t="n">
-        <v>24150</v>
+        <v>87700</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>리보세라닙 담관암 FDA 승인 기대감과 주가 급락 상황 공존. 제약 유증 및 기관외인 매도세.</t>
+          <t>합병 관련 불확실성과 적자 회사 합병에 대한 부정적 전망 및 주가 하락 우려.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['FDA', '담관암', '신약']</t>
+          <t>['합병', '적자', '주가']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -740,7 +740,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>096770</t>
         </is>
       </c>
     </row>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15010</v>
+        <v>14780</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+2.39%</t>
+          <t>'+0.82%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-1.17</v>
       </c>
       <c r="E4" t="n">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="F4" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="G4" t="n">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -794,7 +794,7 @@
         <v>1.17</v>
       </c>
       <c r="O4" t="n">
-        <v>23166844695</v>
+        <v>27427850585</v>
       </c>
       <c r="P4" t="n">
         <v>36200</v>
@@ -803,23 +803,23 @@
         <v>8920</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>-11000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>이란 관련 지정학적 리스크 및 국제유가 상승 기대감 반영. 미국과의 단계적 협상 합의 추진 소식.</t>
+          <t>국제 유가 변동성 및 지정학적 리스크 속 기대와 우려 상존.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['국제유가', '이란', '지정학적 리스크']</t>
+          <t>['국제유가', '지정학적', '변동성']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -839,31 +839,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>139800</v>
+        <v>1709000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+2.27%</t>
+          <t>'+0.71%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.05</v>
+        <v>-0.2</v>
       </c>
       <c r="E5" t="n">
-        <v>72</v>
+        <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>40</v>
+        <v>478</v>
       </c>
       <c r="G5" t="n">
-        <v>134</v>
+        <v>2287</v>
       </c>
       <c r="H5" t="n">
-        <v>15.81</v>
+        <v>50.27</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>136700</v>
+        <v>1697000</v>
       </c>
       <c r="K5" t="n">
-        <v>139500</v>
+        <v>1690000</v>
       </c>
       <c r="L5" t="n">
-        <v>144100</v>
+        <v>1720000</v>
       </c>
       <c r="M5" t="n">
-        <v>138800</v>
+        <v>1685000</v>
       </c>
       <c r="N5" t="n">
-        <v>15.76</v>
+        <v>50.47</v>
       </c>
       <c r="O5" t="n">
-        <v>44119707100</v>
+        <v>884210957000</v>
       </c>
       <c r="P5" t="n">
-        <v>164700</v>
+        <v>2987000</v>
       </c>
       <c r="Q5" t="n">
-        <v>87700</v>
+        <v>325000</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>-47000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>영업이익 10조 전망 및 목표가 상향 리포트 등장, 기술적 반등 기대. 합병 관련 정보와 주가 흔들림.</t>
+          <t>AI 시장 축소 우려 속 반도체 업황 부진 전망과 외인 매도세.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['영업이익', '합병', '리포트']</t>
+          <t>['AI', '반도체', '외인']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>71</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1707000</v>
+        <v>250000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+0.59%</t>
+          <t>'+0.40%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.2</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E6" t="n">
         <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>496</v>
+        <v>481</v>
       </c>
       <c r="G6" t="n">
-        <v>2430</v>
+        <v>2574</v>
       </c>
       <c r="H6" t="n">
-        <v>50.27</v>
+        <v>46.57</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,43 +963,43 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1697000</v>
+        <v>249000</v>
       </c>
       <c r="K6" t="n">
-        <v>1690000</v>
+        <v>248000</v>
       </c>
       <c r="L6" t="n">
-        <v>1713000</v>
+        <v>251500</v>
       </c>
       <c r="M6" t="n">
-        <v>1685000</v>
+        <v>247500</v>
       </c>
       <c r="N6" t="n">
-        <v>50.47</v>
+        <v>46.64</v>
       </c>
       <c r="O6" t="n">
-        <v>662895910500</v>
+        <v>472152957250</v>
       </c>
       <c r="P6" t="n">
-        <v>2987000</v>
+        <v>374500</v>
       </c>
       <c r="Q6" t="n">
-        <v>325000</v>
+        <v>75900</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>-128000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>트럼프 AI 규제 우려 및 미국 10년물 국채 금리 상승에 따른 변동성 예상. 일부 투자자 반등 기대.</t>
+          <t>트럼프 AI 관련 발언에 대한 기대감과 반도체 시장 전망 혼재.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         </is>
       </c>
       <c r="X6" t="n">
-        <v>71</v>
+        <v>106</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>한미반도체</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>249750</v>
+        <v>224250</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+0.30%</t>
+          <t>'-0.33%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.15</v>
       </c>
       <c r="E7" t="n">
-        <v>800</v>
+        <v>95</v>
       </c>
       <c r="F7" t="n">
-        <v>481</v>
+        <v>58</v>
       </c>
       <c r="G7" t="n">
-        <v>2769</v>
+        <v>419</v>
       </c>
       <c r="H7" t="n">
-        <v>46.57</v>
+        <v>7.2</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>249000</v>
+        <v>225000</v>
       </c>
       <c r="K7" t="n">
-        <v>248000</v>
+        <v>228500</v>
       </c>
       <c r="L7" t="n">
-        <v>250000</v>
+        <v>229000</v>
       </c>
       <c r="M7" t="n">
-        <v>247500</v>
+        <v>219500</v>
       </c>
       <c r="N7" t="n">
-        <v>46.64</v>
+        <v>7.05</v>
       </c>
       <c r="O7" t="n">
-        <v>341086649250</v>
+        <v>43668752500</v>
       </c>
       <c r="P7" t="n">
-        <v>374500</v>
+        <v>426000</v>
       </c>
       <c r="Q7" t="n">
-        <v>75900</v>
+        <v>89500</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>-73000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>트럼프 AI 관련 발언과 미국 증시 반등에 따른 국내 증시 및 반도체주 동반 상승 기대. 일부 투자자 반등 예상.</t>
+          <t>머스크 테라팹 공급 계약 체결 뉴스 부각. AI 반도체 관련 성장성 기대감과 함께 공매도 세력과의 공방.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['AI', '반도체', '트럼프']</t>
+          <t>['AI', '반도체', '테라팹']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>106</v>
+        <v>2</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>042700</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>223500</v>
+        <v>85700</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-0.67%</t>
+          <t>'-1.49%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.15</v>
+        <v>-0.11</v>
       </c>
       <c r="E8" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F8" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G8" t="n">
-        <v>396</v>
+        <v>453</v>
       </c>
       <c r="H8" t="n">
-        <v>7.2</v>
+        <v>23.45</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>225000</v>
+        <v>87000</v>
       </c>
       <c r="K8" t="n">
-        <v>228500</v>
+        <v>86200</v>
       </c>
       <c r="L8" t="n">
-        <v>229000</v>
+        <v>86500</v>
       </c>
       <c r="M8" t="n">
-        <v>219500</v>
+        <v>85000</v>
       </c>
       <c r="N8" t="n">
-        <v>7.05</v>
+        <v>23.56</v>
       </c>
       <c r="O8" t="n">
-        <v>34303493750</v>
+        <v>38210028850</v>
       </c>
       <c r="P8" t="n">
-        <v>426000</v>
+        <v>139200</v>
       </c>
       <c r="Q8" t="n">
-        <v>89500</v>
+        <v>57000</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>-81000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>머스크 테라팹 공급 계약 체결 뉴스 부각. AI 반도체 관련 성장성 기대감과 함께 공매도 세력과의 공방.</t>
+          <t>원전 사업 및 엑스에너지 급등에 따른 기대감 반영. 신용 매수 증가.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['AI', '반도체', '테라팹']</t>
+          <t>['원전', '에너지', '신용']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>042700</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>85500</v>
+        <v>10070</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-1.72%</t>
+          <t>'-1.95%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.11</v>
+        <v>0.26</v>
       </c>
       <c r="E9" t="n">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="F9" t="n">
         <v>52</v>
       </c>
       <c r="G9" t="n">
-        <v>437</v>
+        <v>194</v>
       </c>
       <c r="H9" t="n">
-        <v>23.45</v>
+        <v>17.93</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,51 +1239,51 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>87000</v>
+        <v>10270</v>
       </c>
       <c r="K9" t="n">
-        <v>86200</v>
+        <v>11000</v>
       </c>
       <c r="L9" t="n">
-        <v>86500</v>
+        <v>11650</v>
       </c>
       <c r="M9" t="n">
-        <v>85000</v>
+        <v>10050</v>
       </c>
       <c r="N9" t="n">
-        <v>23.56</v>
+        <v>17.67</v>
       </c>
       <c r="O9" t="n">
-        <v>30698139350</v>
+        <v>176877964790</v>
       </c>
       <c r="P9" t="n">
-        <v>139200</v>
+        <v>22450</v>
       </c>
       <c r="Q9" t="n">
-        <v>57000</v>
+        <v>1760</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>-105000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>X에너지 급등 및 원전 관련 긍정적 뉴스에 따른 동반 상승 기대. 원전 ETF 추가 출시 및 신용 매수 유입.</t>
+          <t>미국 광통신주 급등에 따른 기대감 반영. 트럼프 AI 정책 및 기타법인 매수세 유입.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['원전', '에너지', 'ETF']</t>
+          <t>['광통신', 'AI', '기타법인']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14100</v>
+        <v>14070</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.69%</t>
+          <t>'-2.90%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.08</v>
       </c>
       <c r="E10" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="F10" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="G10" t="n">
-        <v>207</v>
+        <v>239</v>
       </c>
       <c r="H10" t="n">
         <v>1.8</v>
@@ -1346,7 +1346,7 @@
         <v>1.88</v>
       </c>
       <c r="O10" t="n">
-        <v>21734815670</v>
+        <v>25656478215</v>
       </c>
       <c r="P10" t="n">
         <v>31500</v>
@@ -1355,23 +1355,23 @@
         <v>1272</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>-33000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>미국 광통신 대장주 루멘텀 폭락 및 국내 증시 하락세 반영. 외국인 보유율이 바닥이라 급락 염려 적음.</t>
+          <t>머니투데이 방송 홍보에도 불구하고 미증시 하락 및 단기 급락에 대한 우려.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['광통신', '미국증시', '외국인']</t>
+          <t>['광통신', '단타', '미증시']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21250</v>
+        <v>21200</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-3.85%</t>
+          <t>'-4.07%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.09</v>
       </c>
       <c r="E11" t="n">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="F11" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="G11" t="n">
-        <v>104</v>
+        <v>134</v>
       </c>
       <c r="H11" t="n">
         <v>28.9</v>
@@ -1438,7 +1438,7 @@
         <v>28.81</v>
       </c>
       <c r="O11" t="n">
-        <v>15122311150</v>
+        <v>19180902825</v>
       </c>
       <c r="P11" t="n">
         <v>35350</v>
@@ -1447,14 +1447,14 @@
         <v>18440</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>-326000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>12억 달러 수주 공시 확인, 코스피 하락 속 주가 상승. 그러나 북극항로 성공 등 뉴스에도 조용하며, 주가 움직임에 대한 불만.</t>
+          <t>12억 달러 규모 수주 공시에도 불구하고 주가 부진 및 불신 심리.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['수주', '공시', '북극항로']</t>
+          <t>['수주', '공시', '주가']</t>
         </is>
       </c>
       <c r="X11" t="n">

--- a/data/trending_integrated_20260915_09.xlsx
+++ b/data/trending_integrated_20260915_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z11"/>
+  <dimension ref="A1:Z12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>31000</v>
+        <v>31100</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+2.14%</t>
+          <t>'+2.47%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.05</v>
       </c>
       <c r="E2" t="n">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="F2" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="G2" t="n">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="H2" t="n">
         <v>17.5</v>
@@ -610,7 +610,7 @@
         <v>17.55</v>
       </c>
       <c r="O2" t="n">
-        <v>2825487750</v>
+        <v>3394136775</v>
       </c>
       <c r="P2" t="n">
         <v>69200</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>138900</v>
+        <v>139100</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+1.61%</t>
+          <t>'+1.76%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.05</v>
       </c>
       <c r="E3" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="F3" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G3" t="n">
-        <v>156</v>
+        <v>188</v>
       </c>
       <c r="H3" t="n">
         <v>15.81</v>
@@ -702,7 +702,7 @@
         <v>15.76</v>
       </c>
       <c r="O3" t="n">
-        <v>51447761500</v>
+        <v>54749680800</v>
       </c>
       <c r="P3" t="n">
         <v>164700</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>합병 관련 불확실성과 적자 회사 합병에 대한 부정적 전망 및 주가 하락 우려.</t>
+          <t>합병 관련 불확실성과 주가 하락 우려. 시가총액 대비 주가 흐름에 대한 불만 표출.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['합병', '적자', '주가']</t>
+          <t>['합병', '적자', '주가 하락']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,83 +747,83 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14780</v>
+        <v>1721000</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+0.82%</t>
+          <t>'+1.41%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-1.17</v>
+        <v>-0.2</v>
       </c>
       <c r="E4" t="n">
-        <v>110</v>
+        <v>800</v>
       </c>
       <c r="F4" t="n">
-        <v>73</v>
+        <v>475</v>
       </c>
       <c r="G4" t="n">
-        <v>253</v>
+        <v>2225</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>50.27</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>14660</v>
+        <v>1697000</v>
       </c>
       <c r="K4" t="n">
-        <v>14980</v>
+        <v>1690000</v>
       </c>
       <c r="L4" t="n">
-        <v>15460</v>
+        <v>1723000</v>
       </c>
       <c r="M4" t="n">
-        <v>14330</v>
+        <v>1685000</v>
       </c>
       <c r="N4" t="n">
-        <v>1.17</v>
+        <v>50.47</v>
       </c>
       <c r="O4" t="n">
-        <v>27427850585</v>
+        <v>1046819927500</v>
       </c>
       <c r="P4" t="n">
-        <v>36200</v>
+        <v>2987000</v>
       </c>
       <c r="Q4" t="n">
-        <v>8920</v>
+        <v>325000</v>
       </c>
       <c r="R4" t="n">
-        <v>-11000</v>
+        <v>-47000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>국제 유가 변동성 및 지정학적 리스크 속 기대와 우려 상존.</t>
+          <t>최악의 순간은 넘겼다는 평가와 함께 상승 기대감. 외국인 매도세 관찰.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['국제유가', '지정학적', '변동성']</t>
+          <t>['반도체', 'AI', '외국인']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>5</v>
+        <v>71</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1709000</v>
+        <v>10360</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+0.71%</t>
+          <t>'+0.88%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.2</v>
+        <v>0.26</v>
       </c>
       <c r="E5" t="n">
-        <v>800</v>
+        <v>78</v>
       </c>
       <c r="F5" t="n">
-        <v>478</v>
+        <v>60</v>
       </c>
       <c r="G5" t="n">
-        <v>2287</v>
+        <v>211</v>
       </c>
       <c r="H5" t="n">
-        <v>50.27</v>
+        <v>17.93</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1697000</v>
+        <v>10270</v>
       </c>
       <c r="K5" t="n">
-        <v>1690000</v>
+        <v>11000</v>
       </c>
       <c r="L5" t="n">
-        <v>1720000</v>
+        <v>11650</v>
       </c>
       <c r="M5" t="n">
-        <v>1685000</v>
+        <v>10010</v>
       </c>
       <c r="N5" t="n">
-        <v>50.47</v>
+        <v>17.67</v>
       </c>
       <c r="O5" t="n">
-        <v>884210957000</v>
+        <v>198434901170</v>
       </c>
       <c r="P5" t="n">
-        <v>2987000</v>
+        <v>22450</v>
       </c>
       <c r="Q5" t="n">
-        <v>325000</v>
+        <v>1760</v>
       </c>
       <c r="R5" t="n">
-        <v>-47000</v>
+        <v>-105000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>AI 시장 축소 우려 속 반도체 업황 부진 전망과 외인 매도세.</t>
+          <t>트럼프 AI 정책 기대감과 미국 광통신 주가 상승에 따른 기대감. 기타법인의 매수세 유입.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['AI', '반도체', '외인']</t>
+          <t>['AI', '광통신', '트럼프']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>71</v>
+        <v>2</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>250000</v>
+        <v>251000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+0.40%</t>
+          <t>'+0.80%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -949,10 +949,10 @@
         <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="G6" t="n">
-        <v>2574</v>
+        <v>2559</v>
       </c>
       <c r="H6" t="n">
         <v>46.57</v>
@@ -978,7 +978,7 @@
         <v>46.64</v>
       </c>
       <c r="O6" t="n">
-        <v>472152957250</v>
+        <v>544996489500</v>
       </c>
       <c r="P6" t="n">
         <v>374500</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>트럼프 AI 관련 발언에 대한 기대감과 반도체 시장 전망 혼재.</t>
+          <t>트럼프 AI 정책 관련 기대와 우려 혼재. 미국 증시 및 반도체 선물 동향 주시.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1023,83 +1023,83 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>224250</v>
+        <v>14720</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-0.33%</t>
+          <t>'+0.41%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.15</v>
+        <v>-1.17</v>
       </c>
       <c r="E7" t="n">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="F7" t="n">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="G7" t="n">
-        <v>419</v>
+        <v>240</v>
       </c>
       <c r="H7" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>225000</v>
+        <v>14660</v>
       </c>
       <c r="K7" t="n">
-        <v>228500</v>
+        <v>14980</v>
       </c>
       <c r="L7" t="n">
-        <v>229000</v>
+        <v>15460</v>
       </c>
       <c r="M7" t="n">
-        <v>219500</v>
+        <v>14330</v>
       </c>
       <c r="N7" t="n">
-        <v>7.05</v>
+        <v>1.17</v>
       </c>
       <c r="O7" t="n">
-        <v>43668752500</v>
+        <v>28923801125</v>
       </c>
       <c r="P7" t="n">
-        <v>426000</v>
+        <v>36200</v>
       </c>
       <c r="Q7" t="n">
-        <v>89500</v>
+        <v>8920</v>
       </c>
       <c r="R7" t="n">
-        <v>-73000</v>
+        <v>-11000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>머스크 테라팹 공급 계약 체결 뉴스 부각. AI 반도체 관련 성장성 기대감과 함께 공매도 세력과의 공방.</t>
+          <t>이란 관련 지정학적 리스크와 국제유가 변동성에 따른 기대와 우려. 헤지주로서의 특징 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['AI', '반도체', '테라팹']</t>
+          <t>['유가', '이란', '지정학']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>042700</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>한미반도체</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>85700</v>
+        <v>225000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-1.49%</t>
+          <t>'+0.00%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.11</v>
+        <v>0.15</v>
       </c>
       <c r="E8" t="n">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="F8" t="n">
         <v>57</v>
       </c>
       <c r="G8" t="n">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="H8" t="n">
-        <v>23.45</v>
+        <v>7.2</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,38 +1147,38 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>87000</v>
+        <v>225000</v>
       </c>
       <c r="K8" t="n">
-        <v>86200</v>
+        <v>228500</v>
       </c>
       <c r="L8" t="n">
-        <v>86500</v>
+        <v>229000</v>
       </c>
       <c r="M8" t="n">
-        <v>85000</v>
+        <v>219500</v>
       </c>
       <c r="N8" t="n">
-        <v>23.56</v>
+        <v>7.05</v>
       </c>
       <c r="O8" t="n">
-        <v>38210028850</v>
+        <v>47572156250</v>
       </c>
       <c r="P8" t="n">
-        <v>139200</v>
+        <v>426000</v>
       </c>
       <c r="Q8" t="n">
-        <v>57000</v>
+        <v>89500</v>
       </c>
       <c r="R8" t="n">
-        <v>-81000</v>
+        <v>-73000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>원전 사업 및 엑스에너지 급등에 따른 기대감 반영. 신용 매수 증가.</t>
+          <t>일론 머스크 테라팹 공급 계약 소식에 대한 기대감. 공매도 세력과의 공방 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,11 +1187,11 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['원전', '에너지', '신용']</t>
+          <t>['테라팹', '머스크', '공매도']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>042700</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10070</v>
+        <v>8750</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-1.95%</t>
+          <t>'-1.13%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="F9" t="n">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="G9" t="n">
-        <v>194</v>
+        <v>166</v>
       </c>
       <c r="H9" t="n">
-        <v>17.93</v>
+        <v>27.16</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,51 +1239,51 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>10270</v>
+        <v>8850</v>
       </c>
       <c r="K9" t="n">
-        <v>11000</v>
+        <v>8750</v>
       </c>
       <c r="L9" t="n">
-        <v>11650</v>
+        <v>8820</v>
       </c>
       <c r="M9" t="n">
-        <v>10050</v>
+        <v>8670</v>
       </c>
       <c r="N9" t="n">
-        <v>17.67</v>
+        <v>27.16</v>
       </c>
       <c r="O9" t="n">
-        <v>176877964790</v>
+        <v>9054113585</v>
       </c>
       <c r="P9" t="n">
-        <v>22450</v>
+        <v>17950</v>
       </c>
       <c r="Q9" t="n">
-        <v>1760</v>
+        <v>8120</v>
       </c>
       <c r="R9" t="n">
-        <v>-105000</v>
+        <v>-351000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>미국 광통신주 급등에 따른 기대감 반영. 트럼프 AI 정책 및 기타법인 매수세 유입.</t>
+          <t>키움증권 목표주가 11000원 제시. 압도적 저평가 주장과 상폐 우려 공존.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['광통신', 'AI', '기타법인']</t>
+          <t>['목표주가', '저평가', '상폐']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,86 +1292,86 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14070</v>
+        <v>85800</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.90%</t>
+          <t>'-1.38%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.08</v>
+        <v>-0.11</v>
       </c>
       <c r="E10" t="n">
-        <v>54</v>
+        <v>96</v>
       </c>
       <c r="F10" t="n">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="G10" t="n">
-        <v>239</v>
+        <v>473</v>
       </c>
       <c r="H10" t="n">
-        <v>1.8</v>
+        <v>23.45</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>14490</v>
+        <v>87000</v>
       </c>
       <c r="K10" t="n">
-        <v>14410</v>
+        <v>86200</v>
       </c>
       <c r="L10" t="n">
-        <v>14600</v>
+        <v>86500</v>
       </c>
       <c r="M10" t="n">
-        <v>13930</v>
+        <v>85000</v>
       </c>
       <c r="N10" t="n">
-        <v>1.88</v>
+        <v>23.56</v>
       </c>
       <c r="O10" t="n">
-        <v>25656478215</v>
+        <v>42349044600</v>
       </c>
       <c r="P10" t="n">
-        <v>31500</v>
+        <v>139200</v>
       </c>
       <c r="Q10" t="n">
-        <v>1272</v>
+        <v>57000</v>
       </c>
       <c r="R10" t="n">
-        <v>-33000</v>
+        <v>-81000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>머니투데이 방송 홍보에도 불구하고 미증시 하락 및 단기 급락에 대한 우려.</t>
+          <t>원전 사업 기대감과 함께 ETF 출시 등 긍정적 요인 부각. 엑스에너지 급등 영향.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['광통신', '단타', '미증시']</t>
+          <t>['원전', '에너지', 'ETF']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1384,97 +1384,189 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21200</v>
+        <v>14040</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-4.07%</t>
+          <t>'-3.11%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="E11" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F11" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G11" t="n">
-        <v>134</v>
+        <v>255</v>
       </c>
       <c r="H11" t="n">
-        <v>28.9</v>
+        <v>1.8</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>22100</v>
+        <v>14490</v>
       </c>
       <c r="K11" t="n">
-        <v>21850</v>
+        <v>14410</v>
       </c>
       <c r="L11" t="n">
-        <v>21850</v>
+        <v>14600</v>
       </c>
       <c r="M11" t="n">
-        <v>21150</v>
+        <v>13930</v>
       </c>
       <c r="N11" t="n">
-        <v>28.81</v>
+        <v>1.88</v>
       </c>
       <c r="O11" t="n">
-        <v>19180902825</v>
+        <v>28687350345</v>
       </c>
       <c r="P11" t="n">
-        <v>35350</v>
+        <v>31500</v>
       </c>
       <c r="Q11" t="n">
-        <v>18440</v>
+        <v>1272</v>
       </c>
       <c r="R11" t="n">
-        <v>-326000</v>
+        <v>-33000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>12억 달러 규모 수주 공시에도 불구하고 주가 부진 및 불신 심리.</t>
+          <t>머니투데이 방송 홍보 효과 기대. 외국인 보유율이 바닥이라 낙폭 제한 예상.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['수주', '공시', '주가']</t>
+          <t>['광통신', '외국인', '낙폭']</t>
         </is>
       </c>
       <c r="X11" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>010170</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>삼성중공업</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>21250</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>'-3.85%</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E12" t="n">
+        <v>61</v>
+      </c>
+      <c r="F12" t="n">
+        <v>40</v>
+      </c>
+      <c r="G12" t="n">
+        <v>146</v>
+      </c>
+      <c r="H12" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>22100</v>
+      </c>
+      <c r="K12" t="n">
+        <v>21850</v>
+      </c>
+      <c r="L12" t="n">
+        <v>21850</v>
+      </c>
+      <c r="M12" t="n">
+        <v>21150</v>
+      </c>
+      <c r="N12" t="n">
+        <v>28.81</v>
+      </c>
+      <c r="O12" t="n">
+        <v>20593072250</v>
+      </c>
+      <c r="P12" t="n">
+        <v>35350</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>18440</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-326000</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>12억 달러 수주 공시에도 주가 부진. 주포와 기관에 대한 불신 제기.</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>['수주', '주가 부진', '기관']</t>
+        </is>
+      </c>
+      <c r="X12" t="n">
         <v>2</v>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>010140</t>
         </is>

--- a/data/trending_integrated_20260915_09.xlsx
+++ b/data/trending_integrated_20260915_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z12"/>
+  <dimension ref="A1:Z13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,79 +563,79 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>31100</v>
+        <v>140400</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+2.47%</t>
+          <t>'+2.71%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.05</v>
+        <v>0.05</v>
       </c>
       <c r="E2" t="n">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="F2" t="n">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="G2" t="n">
-        <v>436</v>
+        <v>198</v>
       </c>
       <c r="H2" t="n">
-        <v>17.5</v>
+        <v>15.81</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>30350</v>
+        <v>136700</v>
       </c>
       <c r="K2" t="n">
-        <v>30250</v>
+        <v>139500</v>
       </c>
       <c r="L2" t="n">
-        <v>31500</v>
+        <v>144100</v>
       </c>
       <c r="M2" t="n">
-        <v>30250</v>
+        <v>138200</v>
       </c>
       <c r="N2" t="n">
-        <v>17.55</v>
+        <v>15.76</v>
       </c>
       <c r="O2" t="n">
-        <v>3394136775</v>
+        <v>59036993700</v>
       </c>
       <c r="P2" t="n">
-        <v>69200</v>
+        <v>164700</v>
       </c>
       <c r="Q2" t="n">
-        <v>24150</v>
+        <v>87700</v>
       </c>
       <c r="R2" t="n">
-        <v>18000</v>
+        <v>38000</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>FDA 승인 관련 불확실성 및 유증 이슈로 인한 주가 하락과 투자자 불신.</t>
+          <t>합병 이슈와 시장 흐름 속에서 주가 변동성에 대한 다양한 의견이 제시되며, 일부는 공매도와 프로그램 매도 등 수급 불안 요인을 지적하고 있습니다. 하지만 일부 투자자들은 긍정적인 실적 전망과 함께 추가 상승 가능성을 언급하고 있습니다.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['FDA', '담관암', '유증']</t>
+          <t>['합병', '적자', '실적']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -648,86 +648,86 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>096770</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>139100</v>
+        <v>31150</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+1.76%</t>
+          <t>'+2.64%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="E3" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F3" t="n">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="G3" t="n">
-        <v>188</v>
+        <v>439</v>
       </c>
       <c r="H3" t="n">
-        <v>15.81</v>
+        <v>17.5</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>136700</v>
+        <v>30350</v>
       </c>
       <c r="K3" t="n">
-        <v>139500</v>
+        <v>30250</v>
       </c>
       <c r="L3" t="n">
-        <v>144100</v>
+        <v>31500</v>
       </c>
       <c r="M3" t="n">
-        <v>138200</v>
+        <v>30250</v>
       </c>
       <c r="N3" t="n">
-        <v>15.76</v>
+        <v>17.55</v>
       </c>
       <c r="O3" t="n">
-        <v>54749680800</v>
+        <v>3606442625</v>
       </c>
       <c r="P3" t="n">
-        <v>164700</v>
+        <v>69200</v>
       </c>
       <c r="Q3" t="n">
-        <v>87700</v>
+        <v>24150</v>
       </c>
       <c r="R3" t="n">
-        <v>35000</v>
+        <v>19000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>합병 관련 불확실성과 주가 하락 우려. 시가총액 대비 주가 흐름에 대한 불만 표출.</t>
+          <t>리보세라닙 FDA 승인 불확실성 및 유증 관련 부정적 전망. 기관 외인 이탈 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['합병', '적자', '주가 하락']</t>
+          <t>['리보세라닙', 'FDA', '유증']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -740,67 +740,67 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1721000</v>
+        <v>14950</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+1.41%</t>
+          <t>'+1.98%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.2</v>
+        <v>-1.17</v>
       </c>
       <c r="E4" t="n">
-        <v>800</v>
+        <v>116</v>
       </c>
       <c r="F4" t="n">
-        <v>475</v>
+        <v>73</v>
       </c>
       <c r="G4" t="n">
-        <v>2225</v>
+        <v>250</v>
       </c>
       <c r="H4" t="n">
-        <v>50.27</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1697000</v>
+        <v>14660</v>
       </c>
       <c r="K4" t="n">
-        <v>1690000</v>
+        <v>14980</v>
       </c>
       <c r="L4" t="n">
-        <v>1723000</v>
+        <v>15460</v>
       </c>
       <c r="M4" t="n">
-        <v>1685000</v>
+        <v>14330</v>
       </c>
       <c r="N4" t="n">
-        <v>50.47</v>
+        <v>1.17</v>
       </c>
       <c r="O4" t="n">
-        <v>1046819927500</v>
+        <v>30762952935</v>
       </c>
       <c r="P4" t="n">
-        <v>2987000</v>
+        <v>36200</v>
       </c>
       <c r="Q4" t="n">
-        <v>325000</v>
+        <v>8920</v>
       </c>
       <c r="R4" t="n">
         <v>-47000</v>
@@ -810,20 +810,20 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>최악의 순간은 넘겼다는 평가와 함께 상승 기대감. 외국인 매도세 관찰.</t>
+          <t>국제유가 상승 요인에도 불구하고 주가 변동성. 이란 관련 지정학적 리스크 주시.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['반도체', 'AI', '외국인']</t>
+          <t>['국제유가', '이란', '지정학적']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>71</v>
+        <v>5</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10360</v>
+        <v>10120</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+0.88%</t>
+          <t>'+1.30%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>78</v>
+        <v>45</v>
       </c>
       <c r="F5" t="n">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="G5" t="n">
-        <v>211</v>
+        <v>56</v>
       </c>
       <c r="H5" t="n">
-        <v>17.93</v>
+        <v>0.6</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>10270</v>
+        <v>9990</v>
       </c>
       <c r="K5" t="n">
-        <v>11000</v>
+        <v>10110</v>
       </c>
       <c r="L5" t="n">
-        <v>11650</v>
+        <v>11390</v>
       </c>
       <c r="M5" t="n">
-        <v>10010</v>
+        <v>10110</v>
       </c>
       <c r="N5" t="n">
-        <v>17.67</v>
+        <v>0.6</v>
       </c>
       <c r="O5" t="n">
-        <v>198434901170</v>
+        <v>127122198610</v>
       </c>
       <c r="P5" t="n">
-        <v>22450</v>
+        <v>15960</v>
       </c>
       <c r="Q5" t="n">
-        <v>1760</v>
+        <v>3500</v>
       </c>
       <c r="R5" t="n">
-        <v>-105000</v>
+        <v>220000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>트럼프 AI 정책 기대감과 미국 광통신 주가 상승에 따른 기대감. 기타법인의 매수세 유입.</t>
+          <t>주가 조작 의혹 및 공매도 관련 부정적 게시글 다수.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['AI', '광통신', '트럼프']</t>
+          <t>['주가조작', '공매도', '미프진']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>004310</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>251000</v>
+        <v>1707000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+0.80%</t>
+          <t>'+0.59%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.2</v>
       </c>
       <c r="E6" t="n">
         <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>480</v>
+        <v>465</v>
       </c>
       <c r="G6" t="n">
-        <v>2559</v>
+        <v>2152</v>
       </c>
       <c r="H6" t="n">
-        <v>46.57</v>
+        <v>50.27</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>249000</v>
+        <v>1697000</v>
       </c>
       <c r="K6" t="n">
-        <v>248000</v>
+        <v>1690000</v>
       </c>
       <c r="L6" t="n">
-        <v>251500</v>
+        <v>1725000</v>
       </c>
       <c r="M6" t="n">
-        <v>247500</v>
+        <v>1685000</v>
       </c>
       <c r="N6" t="n">
-        <v>46.64</v>
+        <v>50.47</v>
       </c>
       <c r="O6" t="n">
-        <v>544996489500</v>
+        <v>1183049614500</v>
       </c>
       <c r="P6" t="n">
-        <v>374500</v>
+        <v>2987000</v>
       </c>
       <c r="Q6" t="n">
-        <v>75900</v>
+        <v>325000</v>
       </c>
       <c r="R6" t="n">
-        <v>-128000</v>
+        <v>-66000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-53000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>트럼프 AI 정책 관련 기대와 우려 혼재. 미국 증시 및 반도체 선물 동향 주시.</t>
+          <t>주주 길들이기 비판 속에서도 조정 끝 기대감 형성. 외인 매수 여부 주시.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['AI', '반도체', '트럼프']</t>
+          <t>['주주', '조정', '외인']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>106</v>
+        <v>71</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,90 +1016,90 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14720</v>
+        <v>10330</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+0.41%</t>
+          <t>'+0.58%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-1.17</v>
+        <v>0.26</v>
       </c>
       <c r="E7" t="n">
-        <v>111</v>
+        <v>83</v>
       </c>
       <c r="F7" t="n">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="G7" t="n">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>17.93</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>14660</v>
+        <v>10270</v>
       </c>
       <c r="K7" t="n">
-        <v>14980</v>
+        <v>11000</v>
       </c>
       <c r="L7" t="n">
-        <v>15460</v>
+        <v>11650</v>
       </c>
       <c r="M7" t="n">
-        <v>14330</v>
+        <v>10010</v>
       </c>
       <c r="N7" t="n">
-        <v>1.17</v>
+        <v>17.67</v>
       </c>
       <c r="O7" t="n">
-        <v>28923801125</v>
+        <v>206693399205</v>
       </c>
       <c r="P7" t="n">
-        <v>36200</v>
+        <v>22450</v>
       </c>
       <c r="Q7" t="n">
-        <v>8920</v>
+        <v>1760</v>
       </c>
       <c r="R7" t="n">
-        <v>-11000</v>
+        <v>303000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>이란 관련 지정학적 리스크와 국제유가 변동성에 따른 기대와 우려. 헤지주로서의 특징 언급.</t>
+          <t>미국 광통신주 급등 및 트럼프 AI 정책 기대감 반영. 기타법인 매수세 유입.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['유가', '이란', '지정학']</t>
+          <t>['광통신', 'AI', '트럼프']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>225000</v>
+        <v>250250</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+0.00%</t>
+          <t>'+0.50%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.15</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>98</v>
+        <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>57</v>
+        <v>478</v>
       </c>
       <c r="G8" t="n">
-        <v>444</v>
+        <v>2385</v>
       </c>
       <c r="H8" t="n">
-        <v>7.2</v>
+        <v>46.57</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>225000</v>
+        <v>249000</v>
       </c>
       <c r="K8" t="n">
-        <v>228500</v>
+        <v>248000</v>
       </c>
       <c r="L8" t="n">
-        <v>229000</v>
+        <v>252000</v>
       </c>
       <c r="M8" t="n">
-        <v>219500</v>
+        <v>247500</v>
       </c>
       <c r="N8" t="n">
-        <v>7.05</v>
+        <v>46.64</v>
       </c>
       <c r="O8" t="n">
-        <v>47572156250</v>
+        <v>638723779250</v>
       </c>
       <c r="P8" t="n">
-        <v>426000</v>
+        <v>374500</v>
       </c>
       <c r="Q8" t="n">
-        <v>89500</v>
+        <v>75900</v>
       </c>
       <c r="R8" t="n">
-        <v>-73000</v>
+        <v>-156000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>-305000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>일론 머스크 테라팹 공급 계약 소식에 대한 기대감. 공매도 세력과의 공방 언급.</t>
+          <t>트럼프 AI 발언 관련 기대감 및 반도체 섹터 동향 주시. 미국 국채 금리 변동성 주시.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['테라팹', '머스크', '공매도']</t>
+          <t>['AI', '반도체', '국채금리']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>2</v>
+        <v>106</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>042700</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>한미반도체</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8750</v>
+        <v>224000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-1.13%</t>
+          <t>'-0.44%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="E9" t="n">
-        <v>45</v>
+        <v>102</v>
       </c>
       <c r="F9" t="n">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="G9" t="n">
-        <v>166</v>
+        <v>474</v>
       </c>
       <c r="H9" t="n">
-        <v>27.16</v>
+        <v>7.2</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,51 +1239,51 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>8850</v>
+        <v>225000</v>
       </c>
       <c r="K9" t="n">
-        <v>8750</v>
+        <v>228500</v>
       </c>
       <c r="L9" t="n">
-        <v>8820</v>
+        <v>229000</v>
       </c>
       <c r="M9" t="n">
-        <v>8670</v>
+        <v>219500</v>
       </c>
       <c r="N9" t="n">
-        <v>27.16</v>
+        <v>7.05</v>
       </c>
       <c r="O9" t="n">
-        <v>9054113585</v>
+        <v>50783247000</v>
       </c>
       <c r="P9" t="n">
-        <v>17950</v>
+        <v>426000</v>
       </c>
       <c r="Q9" t="n">
-        <v>8120</v>
+        <v>89500</v>
       </c>
       <c r="R9" t="n">
-        <v>-351000</v>
+        <v>-102000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>키움증권 목표주가 11000원 제시. 압도적 저평가 주장과 상폐 우려 공존.</t>
+          <t>머스크 테라팹 공급 계약 관련 긍정적 전망. 공매도 세력과의 공방 지속.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['목표주가', '저평가', '상폐']</t>
+          <t>['테라팹', '머스크', '공매도']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>042700</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>85800</v>
+        <v>8760</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-1.38%</t>
+          <t>'-1.02%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.11</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>96</v>
+        <v>49</v>
       </c>
       <c r="F10" t="n">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="G10" t="n">
-        <v>473</v>
+        <v>183</v>
       </c>
       <c r="H10" t="n">
-        <v>23.45</v>
+        <v>27.16</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>87000</v>
+        <v>8850</v>
       </c>
       <c r="K10" t="n">
-        <v>86200</v>
+        <v>8750</v>
       </c>
       <c r="L10" t="n">
-        <v>86500</v>
+        <v>8820</v>
       </c>
       <c r="M10" t="n">
-        <v>85000</v>
+        <v>8670</v>
       </c>
       <c r="N10" t="n">
-        <v>23.56</v>
+        <v>27.16</v>
       </c>
       <c r="O10" t="n">
-        <v>42349044600</v>
+        <v>9705852420</v>
       </c>
       <c r="P10" t="n">
-        <v>139200</v>
+        <v>17950</v>
       </c>
       <c r="Q10" t="n">
-        <v>57000</v>
+        <v>8120</v>
       </c>
       <c r="R10" t="n">
-        <v>-81000</v>
+        <v>-427000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-11000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>원전 사업 기대감과 함께 ETF 출시 등 긍정적 요인 부각. 엑스에너지 급등 영향.</t>
+          <t>적자 지속 및 목표주가 하향 조정 관련 부정적 언급. 경영진 사퇴 요구.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['원전', '에너지', 'ETF']</t>
+          <t>['적자', '목표주가', '경영진']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,86 +1384,86 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14040</v>
+        <v>85600</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-3.11%</t>
+          <t>'-1.61%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.08</v>
+        <v>-0.11</v>
       </c>
       <c r="E11" t="n">
-        <v>56</v>
+        <v>102</v>
       </c>
       <c r="F11" t="n">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="G11" t="n">
-        <v>255</v>
+        <v>483</v>
       </c>
       <c r="H11" t="n">
-        <v>1.8</v>
+        <v>23.45</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>14490</v>
+        <v>87000</v>
       </c>
       <c r="K11" t="n">
-        <v>14410</v>
+        <v>86200</v>
       </c>
       <c r="L11" t="n">
-        <v>14600</v>
+        <v>86500</v>
       </c>
       <c r="M11" t="n">
-        <v>13930</v>
+        <v>85000</v>
       </c>
       <c r="N11" t="n">
-        <v>1.88</v>
+        <v>23.56</v>
       </c>
       <c r="O11" t="n">
-        <v>28687350345</v>
+        <v>46213516900</v>
       </c>
       <c r="P11" t="n">
-        <v>31500</v>
+        <v>139200</v>
       </c>
       <c r="Q11" t="n">
-        <v>1272</v>
+        <v>57000</v>
       </c>
       <c r="R11" t="n">
-        <v>-33000</v>
+        <v>-164000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-62000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>머니투데이 방송 홍보 효과 기대. 외국인 보유율이 바닥이라 낙폭 제한 예상.</t>
+          <t>원전 사업 기대감과 함께 ETF 출시 등 긍정적 요인 부각. 엑스에너지 급등 영향.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['광통신', '외국인', '낙폭']</t>
+          <t>['원전', '에너지', 'ETF']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1476,97 +1476,189 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>21250</v>
+        <v>14070</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-3.85%</t>
+          <t>'-2.90%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="E12" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F12" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G12" t="n">
-        <v>146</v>
+        <v>264</v>
       </c>
       <c r="H12" t="n">
-        <v>28.9</v>
+        <v>1.8</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>22100</v>
+        <v>14490</v>
       </c>
       <c r="K12" t="n">
-        <v>21850</v>
+        <v>14410</v>
       </c>
       <c r="L12" t="n">
-        <v>21850</v>
+        <v>14600</v>
       </c>
       <c r="M12" t="n">
-        <v>21150</v>
+        <v>13930</v>
       </c>
       <c r="N12" t="n">
-        <v>28.81</v>
+        <v>1.88</v>
       </c>
       <c r="O12" t="n">
-        <v>20593072250</v>
+        <v>30404589915</v>
       </c>
       <c r="P12" t="n">
-        <v>35350</v>
+        <v>31500</v>
       </c>
       <c r="Q12" t="n">
-        <v>18440</v>
+        <v>1272</v>
       </c>
       <c r="R12" t="n">
-        <v>-326000</v>
+        <v>6000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-9000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>12억 달러 수주 공시에도 주가 부진. 주포와 기관에 대한 불신 제기.</t>
+          <t>머니투데이 방송 홍보에도 주가 하락. 대선 변수 및 FOMC 금리 등 불확실성 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['수주', '주가 부진', '기관']</t>
+          <t>['홍보', '대선', 'FOMC']</t>
         </is>
       </c>
       <c r="X12" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>010170</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>삼성중공업</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>21200</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>'-4.07%</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E13" t="n">
+        <v>69</v>
+      </c>
+      <c r="F13" t="n">
+        <v>44</v>
+      </c>
+      <c r="G13" t="n">
+        <v>162</v>
+      </c>
+      <c r="H13" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>22100</v>
+      </c>
+      <c r="K13" t="n">
+        <v>21850</v>
+      </c>
+      <c r="L13" t="n">
+        <v>21850</v>
+      </c>
+      <c r="M13" t="n">
+        <v>21150</v>
+      </c>
+      <c r="N13" t="n">
+        <v>28.81</v>
+      </c>
+      <c r="O13" t="n">
+        <v>23422450900</v>
+      </c>
+      <c r="P13" t="n">
+        <v>35350</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>18440</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-616000</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-49000</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>12억 달러 수주 공시 발표에도 주가 부진. 장기 투자에 대한 부정적 의견.</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>['수주', '공시', '장기투자']</t>
+        </is>
+      </c>
+      <c r="X13" t="n">
         <v>2</v>
       </c>
-      <c r="Y12" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>010140</t>
         </is>
